--- a/results/pilot_test/plots/06_gap_table.xlsx
+++ b/results/pilot_test/plots/06_gap_table.xlsx
@@ -834,32 +834,48 @@
           <t>200x10</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
+      <c r="B10" t="n">
+        <v>1919.26</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0</v>
+      </c>
       <c r="D10" t="n">
         <v>1951.78</v>
       </c>
-      <c r="E10" t="inlineStr"/>
+      <c r="E10" t="n">
+        <v>1.741014237905788</v>
+      </c>
       <c r="F10" t="n">
         <v>1925.66</v>
       </c>
-      <c r="G10" t="inlineStr"/>
+      <c r="G10" t="n">
+        <v>0.3834534570887586</v>
+      </c>
       <c r="H10" t="n">
         <v>1961.38</v>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="n">
+        <v>2.243899165510101</v>
+      </c>
       <c r="J10" t="n">
         <v>2012.16</v>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="n">
+        <v>4.886161473592739</v>
+      </c>
       <c r="L10" t="n">
         <v>2063.273333333333</v>
       </c>
-      <c r="M10" t="inlineStr"/>
+      <c r="M10" t="n">
+        <v>7.554402011251781</v>
+      </c>
       <c r="N10" t="n">
         <v>2063.703333333333</v>
       </c>
-      <c r="O10" t="inlineStr"/>
+      <c r="O10" t="n">
+        <v>7.57704615529607</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -867,24 +883,36 @@
           <t>Mk</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
+      <c r="B11" t="n">
+        <v>172.6</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0</v>
+      </c>
       <c r="D11" t="n">
         <v>186.1</v>
       </c>
-      <c r="E11" t="inlineStr"/>
+      <c r="E11" t="n">
+        <v>14.10752537233183</v>
+      </c>
       <c r="F11" t="n">
         <v>268</v>
       </c>
-      <c r="G11" t="inlineStr"/>
+      <c r="G11" t="n">
+        <v>70.12821496062877</v>
+      </c>
       <c r="H11" t="n">
         <v>189.1</v>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="n">
+        <v>16.34450182048575</v>
+      </c>
       <c r="J11" t="n">
         <v>222.6</v>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="n">
+        <v>34.96766082550475</v>
+      </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>

--- a/results/pilot_test/plots/06_gap_table.xlsx
+++ b/results/pilot_test/plots/06_gap_table.xlsx
@@ -884,7 +884,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>172.6</v>
+        <v>173.6</v>
       </c>
       <c r="C11" t="n">
         <v>0</v>
@@ -893,25 +893,25 @@
         <v>186.1</v>
       </c>
       <c r="E11" t="n">
-        <v>14.10752537233183</v>
+        <v>13.50754612890539</v>
       </c>
       <c r="F11" t="n">
         <v>268</v>
       </c>
       <c r="G11" t="n">
-        <v>70.12821496062877</v>
+        <v>69.15552087134421</v>
       </c>
       <c r="H11" t="n">
         <v>189.1</v>
       </c>
       <c r="I11" t="n">
-        <v>16.34450182048575</v>
+        <v>15.72864681198988</v>
       </c>
       <c r="J11" t="n">
         <v>222.6</v>
       </c>
       <c r="K11" t="n">
-        <v>34.96766082550475</v>
+        <v>34.21560430137382</v>
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
